--- a/output/pdf_financials_xlsx/ROI.xlsx
+++ b/output/pdf_financials_xlsx/ROI.xlsx
@@ -1376,7 +1376,7 @@
         <v>0.520275</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.579688</v>
+        <v>-4.895966</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1631,7 +1631,7 @@
         <v>-1.390658</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.737827</v>
+        <v>-2.737827</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>-1.390658</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.737827</v>
+        <v>-2.737827</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.343094</v>
@@ -2348,7 +2348,7 @@
         <v>-27.22622928171736</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>26.8605497606966</v>
+        <v>226.8605497606966</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -2409,7 +2409,7 @@
         <v>-25.4897583321236</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>30.25068107005342</v>
+        <v>-30.25068107005342</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>-6.315310118257217</v>
@@ -6112,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.215024</v>
       </c>
     </row>
     <row r="93">
@@ -6446,7 +6446,7 @@
         <v>-1.390658</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>2.737827</v>
+        <v>-2.737827</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.343094</v>
@@ -6479,10 +6479,10 @@
         <v>-1.718214</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>1.282937</v>
+        <v>-1.282937</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>1.061316</v>
+        <v>-1.061316</v>
       </c>
       <c r="S99" s="3" t="n">
         <v>-0.350758</v>
@@ -11726,7 +11726,11 @@
           <t>Warrant Reserve 11</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -39487,10 +39491,10 @@
         <v>-1.718214</v>
       </c>
       <c r="T293" s="5" t="n">
-        <v>1.282937</v>
+        <v>-1.282937</v>
       </c>
       <c r="U293" s="5" t="n">
-        <v>1.061316</v>
+        <v>-1.061316</v>
       </c>
       <c r="V293" t="inlineStr">
         <is>
@@ -81634,7 +81638,7 @@
         <v>-1.390658</v>
       </c>
       <c r="I698" s="5" t="n">
-        <v>2.737827</v>
+        <v>-2.737827</v>
       </c>
       <c r="J698" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ROI.xlsx
+++ b/output/pdf_financials_xlsx/ROI.xlsx
@@ -1059,19 +1059,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.08122</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012229</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003593</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.578749</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.016669</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000251</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2092,19 +2092,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.446681</v>
+        <v>-5.527901</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.408902</v>
+        <v>-3.421131</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.095242</v>
+        <v>-2.098835</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.910933</v>
+        <v>-2.489682</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.158139</v>
+        <v>2.14147</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.343094</v>
@@ -2116,7 +2116,7 @@
         <v>0.15263</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.329742</v>
+        <v>0.329491</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.609997</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.446681</v>
+        <v>-5.527901</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.408902</v>
+        <v>-3.421131</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.989513</v>
+        <v>-1.993106</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.745482</v>
+        <v>-2.324231</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.338511</v>
+        <v>2.321842</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.082648</v>
@@ -2238,7 +2238,7 @@
         <v>0.586803</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.791143</v>
+        <v>0.790892</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.218196</v>
@@ -2275,19 +2275,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-465.7424525123519</v>
+        <v>-472.6875264010289</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-65.43682592516875</v>
+        <v>-65.67157217021742</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-37.04990111400382</v>
+        <v>-37.11681210915822</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-31.99342638741643</v>
+        <v>-42.60147821968447</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>25.83857579014733</v>
+        <v>25.65439738780244</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-1.521296643642041</v>
@@ -2299,7 +2299,7 @@
         <v>9.172567660236576</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.62295098696366</v>
+        <v>10.61958072305722</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-3.594469226199713</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.120333</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.640045</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.640045</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.120333</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.640045</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.640045</v>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.348806</v>
+        <v>0.228473</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.768675</v>
+        <v>0.12863</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.12863</v>
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">
@@ -62174,7 +62174,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -74362,7 +74362,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -75828,7 +75828,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -80558,7 +80558,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
@@ -81828,7 +81828,7 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
@@ -82784,7 +82784,7 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
@@ -82892,7 +82892,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -86416,7 +86416,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E743" s="5" t="n">

--- a/output/pdf_financials_xlsx/ROI.xlsx
+++ b/output/pdf_financials_xlsx/ROI.xlsx
@@ -1382,10 +1382,10 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.166598</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.575469</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1397,7 +1397,7 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.67315</v>
+        <v>-0.67315</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.003435</v>
@@ -1415,7 +1415,7 @@
         <v>-0.037544</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>-0.033438</v>
+        <v>-0.033437</v>
       </c>
     </row>
     <row r="18">
@@ -1638,15 +1638,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="3" t="n">
+        <v>0.303809</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>-0.422839</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -1830,10 +1826,10 @@
         <v>-0.343094</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.470407</v>
+        <v>0.303809</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.15263</v>
+        <v>-0.422839</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0.329742</v>
@@ -2354,10 +2350,10 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>35.41571447703797</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>377.0353141584223</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0</v>
@@ -2387,7 +2383,7 @@
         <v>-3.667222780072125</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-10.53762763141309</v>
+        <v>-10.53731249212152</v>
       </c>
     </row>
     <row r="32">
@@ -2415,10 +2411,10 @@
         <v>-6.315310118257217</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>7.740025240267935</v>
+        <v>4.998840000723971</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.385824547560099</v>
+        <v>-6.609576530601877</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.427560004124881</v>
@@ -4730,25 +4726,25 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.38948</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.55298</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.377967</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.460523</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.5041369999999999</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.334533</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>0.322455</v>
       </c>
     </row>
     <row r="71">
@@ -4791,25 +4787,25 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.38948</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.55298</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.377967</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.460523</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.5041369999999999</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.334533</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>0.322455</v>
       </c>
     </row>
     <row r="72">
@@ -5035,25 +5031,25 @@
         <v>4.034076</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>9.034852000000001</v>
+        <v>8.645372</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>9.778905</v>
+        <v>9.225925</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>10.562933</v>
+        <v>10.184966</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>8.824726999999999</v>
+        <v>8.364204000000001</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>8.089289000000001</v>
+        <v>7.585152</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>7.573276</v>
+        <v>7.238743</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>7.829126</v>
+        <v>7.506671</v>
       </c>
     </row>
     <row r="76">
@@ -5362,25 +5358,25 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.263319809130113</v>
+        <v>0.660859935185894</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.8129633193991026</v>
+        <v>1.071300966301835</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.495646072924567</v>
+        <v>0.6341971783693311</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.8000823491831912</v>
+        <v>1.060905546506333</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>1.467915358221598</v>
+        <v>2.330653980097374</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>-1.552713648881374</v>
+        <v>-2.424304164202398</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>-0.5563291076112867</v>
+        <v>-1.360384105167616</v>
       </c>
     </row>
     <row r="81">
@@ -6452,10 +6448,10 @@
         <v>-0.343094</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.470407</v>
+        <v>0.303809</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0.15263</v>
+        <v>-0.422839</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>0.329742</v>
@@ -7483,46 +7479,46 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.107862</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.054177</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.018592</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.244817</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.113218</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.176729</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.102302</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.103685</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.109388</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.139886</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.014353</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.467209</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.02782</v>
       </c>
       <c r="S116" s="3" t="n">
-        <v>0</v>
+        <v>-0.166049</v>
       </c>
     </row>
     <row r="117">
@@ -8322,50 +8318,32 @@
       <c r="F129" s="3" t="n">
         <v>-0.48252</v>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>-0.349478</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>-0.485786</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>-0.6947950000000001</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>-0.018659</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>-0.023327</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>0.6219479999999999</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>1.315366</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>0.005505</v>
       </c>
       <c r="P129" s="1" t="inlineStr">
         <is>
@@ -8714,70 +8692,44 @@
       <c r="F135" s="3" t="n">
         <v>1.258012</v>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>-0.000388</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>1.201028</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>0.448943</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>1.586741</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>-0.641078</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0.419463</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>0.328228</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>0.256275</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>1.0467</v>
+      </c>
+      <c r="P135" s="3" t="n">
+        <v>0.602272</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>0.686819</v>
+      </c>
+      <c r="R135" s="3" t="n">
+        <v>0.887522</v>
+      </c>
+      <c r="S135" s="3" t="n">
+        <v>0.455033</v>
       </c>
     </row>
   </sheetData>
@@ -10664,7 +10616,11 @@
           <t>Lease liabilities 4</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -15760,7 +15716,11 @@
           <t>Lease liabilities 4 460,523</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -20784,7 +20744,11 @@
           <t>Lease liabilities 2,5</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -37604,7 +37568,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -37806,7 +37774,11 @@
           <t>Acquisition of intangible assets 6</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -41026,7 +40998,11 @@
           <t>Net cash generated by operating activities</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -41804,7 +41780,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -43902,7 +43882,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -52246,7 +52230,11 @@
           <t>Acquisition of intangible assets 5</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -52868,7 +52856,11 @@
           <t>Deferred tax recovery 17</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -53492,7 +53484,11 @@
           <t>Payment for acquisition of intangible assets 6</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -55168,7 +55164,11 @@
           <t>Net cash generated in operating activities</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -56342,7 +56342,11 @@
           <t>Net cash generated (used in) operating activities</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -62774,7 +62778,11 @@
           <t>Income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
@@ -65052,7 +65060,11 @@
           <t>Expected income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -65684,7 +65696,11 @@
           <t>Income tax (recovery)</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -69526,7 +69542,11 @@
           <t>Income tax (recovery) expense 16</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>-</t>
@@ -70666,7 +70686,11 @@
           <t>Income tax (recovery) expense 21</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
           <t>-</t>
@@ -71936,7 +71960,11 @@
           <t>Income tax (recovery) expense 22</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E606" t="inlineStr">
         <is>
           <t>-</t>
@@ -73306,7 +73334,11 @@
           <t>Income tax recovery 24</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
@@ -76256,7 +76288,11 @@
           <t>Income tax recovery 17</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E647" t="inlineStr">
         <is>
           <t>-</t>
@@ -77516,7 +77552,11 @@
           <t>Income tax recovery 16</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
@@ -78562,7 +78602,11 @@
           <t>Income tax recovery 17</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
           <t>-</t>
@@ -79410,7 +79454,11 @@
           <t>Income tax recovery 17</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E677" t="inlineStr">
         <is>
           <t>-</t>
